--- a/data/original/overwork01.xlsx
+++ b/data/original/overwork01.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
-  <si>
-    <t>筛选条件： 发起时间：2025-07-01 到 2025-08-01 类型：加班 状态：全部 统计：共 23 条审批（编号相同的审批单据计算为一条）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="271">
+  <si>
+    <t>筛选条件： 发起时间：2025-07-27 到 2025-09-02 类型：加班 状态：全部 统计：共 33 条审批（编号相同的审批单据计算为一条）</t>
   </si>
   <si>
     <t>申请编号</t>
@@ -94,7 +94,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>202507020002</t>
+    <t>202508020001</t>
   </si>
   <si>
     <t>已同意</t>
@@ -103,544 +103,730 @@
     <t/>
   </si>
   <si>
+    <t>dad88d24</t>
+  </si>
+  <si>
+    <t>桂治国</t>
+  </si>
+  <si>
+    <t>产品中心/系统开发部</t>
+  </si>
+  <si>
+    <t>32114e27ega71f85</t>
+  </si>
+  <si>
+    <t>朱显斌</t>
+  </si>
+  <si>
+    <t>朱显斌;雷继彬</t>
+  </si>
+  <si>
+    <t>桂治国|发起审批|2025-08-02 08:17:40;朱显斌|同意|2025-08-02 09:04:45;雷继彬|同意|2025-08-02 14:40:17</t>
+  </si>
+  <si>
+    <t>6h22m38.21s</t>
+  </si>
+  <si>
+    <t>2025年08月02日</t>
+  </si>
+  <si>
+    <t>加班1</t>
+  </si>
+  <si>
+    <t>2025年08月02日 09:00</t>
+  </si>
+  <si>
+    <t>2025年08月02日 18:20</t>
+  </si>
+  <si>
+    <t>9.3</t>
+  </si>
+  <si>
+    <t>桥壳图纸设计</t>
+  </si>
+  <si>
+    <t>202508020011</t>
+  </si>
+  <si>
+    <t>d9845775</t>
+  </si>
+  <si>
+    <t>叶旭</t>
+  </si>
+  <si>
+    <t>制造中心/仓储物流部</t>
+  </si>
+  <si>
+    <t>aceg73d6d23cdebc</t>
+  </si>
+  <si>
+    <t>张健宁</t>
+  </si>
+  <si>
+    <t>张健宁;杜鸣</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-02 19:23:27;张健宁|同意|2025-08-03 12:09:17;杜鸣|同意|2025-08-04 10:22:11</t>
+  </si>
+  <si>
+    <t>38h58m43.118s</t>
+  </si>
+  <si>
+    <t>2025年08月01日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月01日 21:00</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>发货</t>
+  </si>
+  <si>
+    <t>202507300045</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-07-30 17:35:17;张健宁|同意|2025-07-30 18:49:22;杜鸣|同意|2025-07-31 08:18:11</t>
+  </si>
+  <si>
+    <t>14h42m53.961s</t>
+  </si>
+  <si>
+    <t>2025年07月30日</t>
+  </si>
+  <si>
+    <t>2025年07月29日 18:00</t>
+  </si>
+  <si>
+    <t>2025年07月29日 19:00</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>202508020012</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-02 19:23:51;张健宁|同意|2025-08-03 12:09:23;杜鸣|同意|2025-08-04 10:22:17</t>
+  </si>
+  <si>
+    <t>38h58m25.821s</t>
+  </si>
+  <si>
+    <t>2025年08月02日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月02日 19:00</t>
+  </si>
+  <si>
+    <t>202507270004</t>
+  </si>
+  <si>
+    <t>9a282a5e</t>
+  </si>
+  <si>
+    <t>朱泽利</t>
+  </si>
+  <si>
+    <t>产品中心/AIO开发部</t>
+  </si>
+  <si>
+    <t>54744g6c6edgb9cf</t>
+  </si>
+  <si>
+    <t>石丁哲</t>
+  </si>
+  <si>
+    <t>石丁哲;雷继彬</t>
+  </si>
+  <si>
+    <t>朱泽利|发起审批|2025-07-27 18:41:44;石丁哲|同意|2025-07-28 17:08:23;雷继彬|同意|2025-07-29 08:38:57</t>
+  </si>
+  <si>
+    <t>37h57m13.524s</t>
+  </si>
+  <si>
+    <t>2025年07月27日</t>
+  </si>
+  <si>
+    <t>2025年07月27日 12:00</t>
+  </si>
+  <si>
+    <t>2025年07月27日 17:00</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>跟十堰田总前往襄阳中车集团公司总结凌特样车的遗留历史问题</t>
+  </si>
+  <si>
+    <t>202508030005</t>
+  </si>
+  <si>
     <t>462a1a3e</t>
   </si>
   <si>
     <t>李运动</t>
   </si>
   <si>
-    <t>制造中心/仓储物流部</t>
-  </si>
-  <si>
-    <t>aceg73d6d23cdebc</t>
-  </si>
-  <si>
-    <t>张健宁</t>
-  </si>
-  <si>
-    <t>张健宁;杜鸣</t>
-  </si>
-  <si>
-    <t>李运动|发起审批|2025-07-02 08:19:19;张健宁|同意|2025-07-02 10:50:58;杜鸣|同意|2025-07-02 14:26:18</t>
-  </si>
-  <si>
-    <t>6h6m59.506s</t>
-  </si>
-  <si>
-    <t>2025年07月02日</t>
-  </si>
-  <si>
-    <t>加班1</t>
-  </si>
-  <si>
-    <t>2025年07月01日 18:30</t>
-  </si>
-  <si>
-    <t>2025年07月01日 21:00</t>
+    <t>李运动|发起审批|2025-08-03 15:39:25;张健宁|同意|2025-08-04 14:49:03;杜鸣|同意|2025-08-04 16:32:30</t>
+  </si>
+  <si>
+    <t>24h53m5.59s</t>
+  </si>
+  <si>
+    <t>2025年08月03日</t>
+  </si>
+  <si>
+    <t>2025年07月31日 18:00</t>
+  </si>
+  <si>
+    <t>2025年07月31日 20:00</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>仓库搬迁，物料整理</t>
+  </si>
+  <si>
+    <t>202507300002</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-07-30 08:41:40;张健宁|同意|2025-07-30 09:25:00;杜鸣|同意|2025-07-31 08:17:53</t>
+  </si>
+  <si>
+    <t>23h36m13.486s</t>
+  </si>
+  <si>
+    <t>2025年07月28日 18:00</t>
+  </si>
+  <si>
+    <t>2025年07月28日 19:00</t>
+  </si>
+  <si>
+    <t>日常账务处理</t>
+  </si>
+  <si>
+    <t>加班2</t>
+  </si>
+  <si>
+    <t>2025年07月29日 20:00</t>
+  </si>
+  <si>
+    <t>202507280045</t>
+  </si>
+  <si>
+    <t>eec52f77</t>
+  </si>
+  <si>
+    <t>杜锋</t>
+  </si>
+  <si>
+    <t>质量保证部</t>
+  </si>
+  <si>
+    <t>6g81a528518e967g</t>
+  </si>
+  <si>
+    <t>李锋;张成林</t>
+  </si>
+  <si>
+    <t>杜锋|发起审批|2025-07-28 18:37:16;李锋|同意|2025-07-28 18:42:48;张成林|同意|2025-07-29 11:05:25</t>
+  </si>
+  <si>
+    <t>16h28m8.679s</t>
+  </si>
+  <si>
+    <t>2025年07月28日</t>
+  </si>
+  <si>
+    <t>2025年07月28日 17:30</t>
+  </si>
+  <si>
+    <t>2025年07月28日 18:30</t>
+  </si>
+  <si>
+    <t>加班开会</t>
+  </si>
+  <si>
+    <t>202508070034</t>
+  </si>
+  <si>
+    <t>已撤回</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-07 18:07:08</t>
+  </si>
+  <si>
+    <t>8.874s</t>
+  </si>
+  <si>
+    <t>2025年08月07日</t>
+  </si>
+  <si>
+    <t>2025年08月07日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月07日 21:00</t>
+  </si>
+  <si>
+    <t>202508070032</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-07 18:06:05</t>
+  </si>
+  <si>
+    <t>24.185s</t>
+  </si>
+  <si>
+    <t>2025年08月06日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月06日 20:00</t>
+  </si>
+  <si>
+    <t>搬仓库</t>
+  </si>
+  <si>
+    <t>202508070033</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-07 18:06:42;张健宁|同意|2025-08-07 19:43:17;杜鸣|同意|2025-08-07 21:08:35</t>
+  </si>
+  <si>
+    <t>3h1m53.263s</t>
+  </si>
+  <si>
+    <t>2025年08月05日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月05日 20:00</t>
+  </si>
+  <si>
+    <t>202508030006</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-08-03 15:42:33;张健宁|同意|2025-08-04 14:48:56;杜鸣|同意|2025-08-04 16:32:41</t>
+  </si>
+  <si>
+    <t>24h50m8.384s</t>
+  </si>
+  <si>
+    <t>2025年08月01日 20:00</t>
+  </si>
+  <si>
+    <t>加班3</t>
+  </si>
+  <si>
+    <t>2025年08月02日 08:30</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>202508070035</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-07 18:07:31;张健宁|同意|2025-08-07 19:43:13;杜鸣|同意|2025-08-07 21:08:41</t>
+  </si>
+  <si>
+    <t>3h1m10.288s</t>
+  </si>
+  <si>
+    <t>2025年08月06日 21:00</t>
+  </si>
+  <si>
+    <t>202508090030</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-08-09 18:02:14;张健宁|同意|2025-08-09 18:17:50;杜鸣|同意|2025-08-11 15:00:37</t>
+  </si>
+  <si>
+    <t>44h58m23.191s</t>
+  </si>
+  <si>
+    <t>2025年08月09日</t>
+  </si>
+  <si>
+    <t>2025年08月08日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月08日 19:00</t>
+  </si>
+  <si>
+    <t>仓库账务处理</t>
+  </si>
+  <si>
+    <t>202508070001</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-08-07 08:28:12;张健宁|同意|2025-08-07 15:04:34;杜鸣|同意|2025-08-07 19:08:50</t>
+  </si>
+  <si>
+    <t>10h40m37.219s</t>
+  </si>
+  <si>
+    <t>2025年08月04日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月04日 20:00</t>
+  </si>
+  <si>
+    <t>仓库搬迁，账务处理</t>
+  </si>
+  <si>
+    <t>202508090032</t>
+  </si>
+  <si>
+    <t>fb7adb73</t>
+  </si>
+  <si>
+    <t>梁梅</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-08-09 18:55:26;张健宁|同意|2025-08-09 18:55:33;杜鸣|同意|2025-08-11 15:00:25</t>
+  </si>
+  <si>
+    <t>44h4m59.087s</t>
+  </si>
+  <si>
+    <t>2025年08月09日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月09日 19:00</t>
+  </si>
+  <si>
+    <t>物流发运整理及周度汇报资料准备</t>
+  </si>
+  <si>
+    <t>202508150001</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-15 08:24:07;张健宁|同意|2025-08-15 13:58:34;杜鸣|同意|2025-08-15 14:18:16</t>
+  </si>
+  <si>
+    <t>5h54m8.896s</t>
+  </si>
+  <si>
+    <t>2025年08月15日</t>
+  </si>
+  <si>
+    <t>2025年08月14日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月14日 20:00</t>
+  </si>
+  <si>
+    <t>202508130030</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-13 18:11:35;张健宁|同意|2025-08-13 22:52:58;杜鸣|同意|2025-08-14 10:20:17</t>
+  </si>
+  <si>
+    <t>16h8m41.859s</t>
+  </si>
+  <si>
+    <t>2025年08月13日</t>
+  </si>
+  <si>
+    <t>2025年08月12日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月12日 20:00</t>
+  </si>
+  <si>
+    <t>202508090033</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-09 20:49:31;张健宁|同意|2025-08-10 23:03:36;杜鸣|同意|2025-08-10 23:04:01</t>
+  </si>
+  <si>
+    <t>26h14m30.306s</t>
+  </si>
+  <si>
+    <t>2025年08月08日 20:00</t>
+  </si>
+  <si>
+    <t>202508110045</t>
+  </si>
+  <si>
+    <t>c617e425</t>
+  </si>
+  <si>
+    <t>李淑娜</t>
+  </si>
+  <si>
+    <t>桂治国;朱显斌;雷继彬</t>
+  </si>
+  <si>
+    <t>李淑娜|发起审批|2025-08-11 20:06:41;桂治国|同意|2025-08-11 20:07:55;朱显斌|同意|2025-08-11 20:08:27;雷继彬|同意|2025-08-12 10:21:00</t>
+  </si>
+  <si>
+    <t>14h14m20.226s</t>
+  </si>
+  <si>
+    <t>2025年08月11日</t>
+  </si>
+  <si>
+    <t>2025年08月11日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月11日 20:00</t>
+  </si>
+  <si>
+    <t>组织周会并撰写发布会议纪要</t>
+  </si>
+  <si>
+    <t>202508160004</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-08-16 10:58:48</t>
+  </si>
+  <si>
+    <t>1h37m34.41s</t>
+  </si>
+  <si>
+    <t>2025年08月16日</t>
+  </si>
+  <si>
+    <t>2025年08月16日 08:30</t>
+  </si>
+  <si>
+    <t>2025年08月16日 18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 有生产任务，保障生产加班</t>
+  </si>
+  <si>
+    <t>202508160006</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-08-16 12:37:39</t>
+  </si>
+  <si>
+    <t>2m39.462s</t>
+  </si>
+  <si>
+    <t>2025年08月16日 12:00</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  有生产任务，保障生产加班</t>
+  </si>
+  <si>
+    <t>202508130032</t>
+  </si>
+  <si>
+    <t>李淑娜|发起审批|2025-08-13 18:19:32;桂治国|同意|2025-08-13 18:22:07;朱显斌|同意|2025-08-13 18:24:28;雷继彬|同意|2025-08-13 18:33:43</t>
+  </si>
+  <si>
+    <t>14m11.841s</t>
+  </si>
+  <si>
+    <t>2025年08月12日 18:30</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>柱塞泵版本取力器支架出图</t>
+  </si>
+  <si>
+    <t>202508160001</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-08-16 07:58:02</t>
+  </si>
+  <si>
+    <t>3h0m17.328s</t>
+  </si>
+  <si>
+    <t>202508160007</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-08-16 12:40:29;张健宁|同意|2025-08-16 17:59:52;杜鸣|同意|2025-08-18 10:45:49</t>
+  </si>
+  <si>
+    <t>46h5m20.412s</t>
+  </si>
+  <si>
+    <t>202508200002</t>
+  </si>
+  <si>
+    <t>叶旭|发起审批|2025-08-20 08:30:28;张健宁|同意|2025-08-20 09:07:18;杜鸣|同意|2025-08-20 09:07:45</t>
+  </si>
+  <si>
+    <t>37m17.484s</t>
+  </si>
+  <si>
+    <t>2025年08月20日</t>
+  </si>
+  <si>
+    <t>2025年08月18日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月18日 19:00</t>
+  </si>
+  <si>
+    <t>202508160013</t>
+  </si>
+  <si>
+    <t>c252fg26</t>
+  </si>
+  <si>
+    <t>张喆</t>
+  </si>
+  <si>
+    <t>张喆|发起审批|2025-08-16 21:14:58</t>
+  </si>
+  <si>
+    <t>85h12m43.751s</t>
+  </si>
+  <si>
+    <t>2025年08月16日 10:00</t>
+  </si>
+  <si>
+    <t>2025年08月16日 16:00</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>绘制导向套管、导向叉形臂、导向销轴2维图纸</t>
+  </si>
+  <si>
+    <t>202508200004</t>
+  </si>
+  <si>
+    <t>李运动|发起审批|2025-08-20 09:23:11;张健宁|同意|2025-08-20 09:34:41;杜鸣|同意|2025-08-20 09:59:16</t>
+  </si>
+  <si>
+    <t>36m5.147s</t>
+  </si>
+  <si>
+    <t>2025年08月19日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月19日 19:00</t>
+  </si>
+  <si>
+    <t>账务处理</t>
+  </si>
+  <si>
+    <t>202508250031</t>
+  </si>
+  <si>
+    <t>李淑娜|发起审批|2025-08-25 21:04:13;桂治国|同意|2025-08-25 21:16:21;朱显斌|同意|2025-08-26 08:36:37;雷继彬|同意|2025-08-26 08:48:44</t>
+  </si>
+  <si>
+    <t>11h44m31.247s</t>
+  </si>
+  <si>
+    <t>2025年08月25日</t>
+  </si>
+  <si>
+    <t>2025年08月25日 18:01</t>
+  </si>
+  <si>
+    <t>2025年08月25日 20:30</t>
   </si>
   <si>
     <t>2.5</t>
   </si>
   <si>
-    <t>统计整理杭州及随州生产线边退库物料清单并做调拨单据</t>
-  </si>
-  <si>
-    <t>202507100020</t>
-  </si>
-  <si>
-    <t>已撤回</t>
-  </si>
-  <si>
-    <t>eec52f77</t>
-  </si>
-  <si>
-    <t>杜锋</t>
-  </si>
-  <si>
-    <t>质量保证部</t>
-  </si>
-  <si>
-    <t>6g81a528518e967g</t>
-  </si>
-  <si>
-    <t>张成林</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-10 17:04:05</t>
-  </si>
-  <si>
-    <t>53.557s</t>
-  </si>
-  <si>
-    <t>2025年03月20日</t>
-  </si>
-  <si>
-    <t>2025年07月10日 17:30</t>
-  </si>
-  <si>
-    <t>2025年07月10日 19:00</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>零部件检验</t>
-  </si>
-  <si>
-    <t>202507020031</t>
-  </si>
-  <si>
-    <t>fb7adb73</t>
-  </si>
-  <si>
-    <t>梁梅</t>
-  </si>
-  <si>
-    <t>梁梅|发起审批|2025-07-02 16:42:35;张健宁|同意|2025-07-02 17:33:53;杜鸣|同意|2025-07-02 20:14:50</t>
-  </si>
-  <si>
-    <t>3h32m14.808s</t>
-  </si>
-  <si>
-    <t>2025年07月01日</t>
-  </si>
-  <si>
-    <t>新系统切换账务转结工作</t>
-  </si>
-  <si>
-    <t>202507030024</t>
-  </si>
-  <si>
-    <t>梁梅|发起审批|2025-07-03 13:59:01;张健宁|同意|2025-07-03 13:59:17;杜鸣|同意|2025-07-03 14:00:24</t>
-  </si>
-  <si>
-    <t>1m23.664s</t>
-  </si>
-  <si>
-    <t>2025年07月02日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月02日 19:00</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>积压专项处理接待回收供应商</t>
-  </si>
-  <si>
-    <t>202507090034</t>
-  </si>
-  <si>
-    <t>d9845775</t>
-  </si>
-  <si>
-    <t>叶旭</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-09 18:09:39;张健宁|同意|2025-07-09 22:43:15;杜鸣|同意|2025-07-10 08:23:52</t>
-  </si>
-  <si>
-    <t>14h14m12.944s</t>
-  </si>
-  <si>
-    <t>2025年07月09日</t>
-  </si>
-  <si>
-    <t>2025年07月08日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月08日 21:00</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>发货</t>
-  </si>
-  <si>
-    <t>202507050001</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-05 07:45:38;张健宁|同意|2025-07-05 11:00:31;杜鸣|同意|2025-07-05 16:07:20</t>
-  </si>
-  <si>
-    <t>8h21m41.902s</t>
-  </si>
-  <si>
-    <t>2025年07月05日</t>
-  </si>
-  <si>
-    <t>2025年07月04日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月04日 20:00</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>法国</t>
-  </si>
-  <si>
-    <t>202507050003</t>
-  </si>
-  <si>
-    <t>cc3fac3e</t>
-  </si>
-  <si>
-    <t>朱隆轩</t>
-  </si>
-  <si>
-    <t>产品中心/AIO开发部</t>
-  </si>
-  <si>
-    <t>54744g6c6edgb9cf</t>
-  </si>
-  <si>
-    <t>石丁哲</t>
-  </si>
-  <si>
-    <t>朱隆轩|发起审批|2025-07-05 08:40:45</t>
-  </si>
-  <si>
-    <t>51h1m30.257s</t>
-  </si>
-  <si>
-    <t>2025年07月05日 08:30</t>
-  </si>
-  <si>
-    <t>2025年07月05日 18:00</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>海珀特ET2.0软件DCU故障测试</t>
-  </si>
-  <si>
-    <t>202507100021</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-10 17:06:27</t>
-  </si>
-  <si>
-    <t>15m22.182s</t>
-  </si>
-  <si>
-    <t>2025年03月20日 17:30</t>
-  </si>
-  <si>
-    <t>2025年03月20日 19:00</t>
-  </si>
-  <si>
-    <t>202507100023</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-10 17:09:33</t>
-  </si>
-  <si>
-    <t>11m57.575s</t>
-  </si>
-  <si>
-    <t>2025年03月21日</t>
-  </si>
-  <si>
-    <t>2025年03月22日 17:30</t>
-  </si>
-  <si>
-    <t>2025年03月22日 19:00</t>
-  </si>
-  <si>
-    <t>202507100024</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-10 17:11:41</t>
-  </si>
-  <si>
-    <t>9m35.196s</t>
-  </si>
-  <si>
-    <t>2025年03月23日</t>
-  </si>
-  <si>
-    <t>2025年03月23日 10:00</t>
-  </si>
-  <si>
-    <t>2025年03月23日 16:00</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>202507170021</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-17 18:06:15;张健宁|同意|2025-07-17 18:16:52;杜鸣|同意|2025-07-18 08:52:57</t>
-  </si>
-  <si>
-    <t>14h46m41.435s</t>
-  </si>
-  <si>
-    <t>2025年07月17日</t>
-  </si>
-  <si>
-    <t>2025年07月16日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月16日 20:00</t>
-  </si>
-  <si>
-    <t>202507120036</t>
-  </si>
-  <si>
-    <t>李运动|发起审批|2025-07-12 20:22:45;张健宁|同意|2025-07-13 19:50:11;杜鸣|同意|2025-07-13 21:42:46</t>
-  </si>
-  <si>
-    <t>25h20m1.39s</t>
-  </si>
-  <si>
-    <t>2025年07月12日</t>
-  </si>
-  <si>
-    <t>2025年07月11日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月11日 20:00</t>
-  </si>
-  <si>
-    <t>杭州仓库生产物料发随州备用，打包装车。</t>
-  </si>
-  <si>
-    <t>202507230001</t>
-  </si>
-  <si>
-    <t>梁梅|发起审批|2025-07-23 08:49:23;张健宁|同意|2025-07-23 10:09:51;杜鸣|同意|2025-07-23 15:12:18</t>
-  </si>
-  <si>
-    <t>6h22m54.853s</t>
-  </si>
-  <si>
-    <t>2025年07月22日</t>
-  </si>
-  <si>
-    <t>2025年07月22日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月22日 19:00</t>
-  </si>
-  <si>
-    <t>仓储账务处理</t>
-  </si>
-  <si>
-    <t>202507240006</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-24 10:30:09;张健宁|同意|2025-07-24 11:03:23;杜鸣|同意|2025-07-24 15:51:15</t>
-  </si>
-  <si>
-    <t>5h21m6.426s</t>
-  </si>
-  <si>
-    <t>2025年07月24日</t>
-  </si>
-  <si>
-    <t>2025年07月23日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月23日 21:00</t>
-  </si>
-  <si>
-    <t>202507100022</t>
-  </si>
-  <si>
-    <t>李锋</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-10 17:08:17;李锋|同意|"同意" |2025-07-10 17:09:27;李锋|评论|"@杜锋杜工，几个月前的加班，怎么下载才申请" |2025-07-10 17:11:23</t>
-  </si>
-  <si>
-    <t>13m22.43s</t>
-  </si>
-  <si>
-    <t>2025年03月21日 17:30</t>
-  </si>
-  <si>
-    <t>2025年03月21日 19:00</t>
-  </si>
-  <si>
-    <t>检验与记录</t>
-  </si>
-  <si>
-    <t>202507240030</t>
-  </si>
-  <si>
-    <t>梁梅|发起审批|2025-07-24 18:28:35;张健宁|同意|2025-07-24 19:28:18;杜鸣|同意|2025-07-25 15:36:57</t>
-  </si>
-  <si>
-    <t>21h8m22.378s</t>
-  </si>
-  <si>
-    <t>2025年07月23日</t>
-  </si>
-  <si>
-    <t>2025年07月23日 20:00</t>
-  </si>
-  <si>
-    <t>协调EA1900N项目加急物料到货检验、发生产总装</t>
-  </si>
-  <si>
-    <t>202507120038</t>
-  </si>
-  <si>
-    <t>5e21ef5b</t>
-  </si>
-  <si>
-    <t>李黎</t>
-  </si>
-  <si>
-    <t>李锋;张成林</t>
-  </si>
-  <si>
-    <t>李黎|发起审批|2025-07-12 23:35:18;李锋|同意|"确认" |2025-07-13 09:53:22;张成林|同意|2025-07-13 10:25:34</t>
-  </si>
-  <si>
-    <t>10h50m15.816s</t>
-  </si>
-  <si>
-    <t>2025年07月12日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月12日 23:30</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>蒙城处理京深车辆问题</t>
-  </si>
-  <si>
-    <t>202507250004</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-25 09:16:58;张健宁|同意|2025-07-25 12:26:42;杜鸣|同意|2025-07-25 15:36:35</t>
-  </si>
-  <si>
-    <t>6h19m37.155s</t>
-  </si>
-  <si>
-    <t>2025年07月25日</t>
-  </si>
-  <si>
-    <t>2025年07月24日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月24日 20:00</t>
-  </si>
-  <si>
-    <t>202507240034</t>
-  </si>
-  <si>
-    <t>梁梅|发起审批|2025-07-24 20:17:20;张健宁|同意|2025-07-24 20:55:30;杜鸣|同意|2025-07-25 15:36:52</t>
-  </si>
-  <si>
-    <t>19h19m33.012s</t>
-  </si>
-  <si>
-    <t>202507300002</t>
-  </si>
-  <si>
-    <t>李运动|发起审批|2025-07-30 08:41:40;张健宁|同意|2025-07-30 09:25:00;杜鸣|同意|2025-07-31 08:17:53</t>
-  </si>
-  <si>
-    <t>23h36m13.486s</t>
-  </si>
-  <si>
-    <t>2025年07月30日</t>
-  </si>
-  <si>
-    <t>2025年07月28日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月28日 19:00</t>
-  </si>
-  <si>
-    <t>日常账务处理</t>
-  </si>
-  <si>
-    <t>加班2</t>
-  </si>
-  <si>
-    <t>2025年07月29日 18:00</t>
-  </si>
-  <si>
-    <t>2025年07月29日 20:00</t>
-  </si>
-  <si>
-    <t>202507280045</t>
-  </si>
-  <si>
-    <t>杜锋|发起审批|2025-07-28 18:37:16;李锋|同意|2025-07-28 18:42:48;张成林|同意|2025-07-29 11:05:25</t>
-  </si>
-  <si>
-    <t>16h28m8.679s</t>
-  </si>
-  <si>
-    <t>2025年07月28日</t>
-  </si>
-  <si>
-    <t>2025年07月28日 17:30</t>
-  </si>
-  <si>
-    <t>2025年07月28日 18:30</t>
-  </si>
-  <si>
-    <t>加班开会</t>
-  </si>
-  <si>
-    <t>202507270004</t>
-  </si>
-  <si>
-    <t>9a282a5e</t>
-  </si>
-  <si>
-    <t>朱泽利</t>
-  </si>
-  <si>
-    <t>石丁哲;雷继彬</t>
-  </si>
-  <si>
-    <t>朱泽利|发起审批|2025-07-27 18:41:44;石丁哲|同意|2025-07-28 17:08:23;雷继彬|同意|2025-07-29 08:38:57</t>
-  </si>
-  <si>
-    <t>37h57m13.524s</t>
-  </si>
-  <si>
-    <t>2025年07月27日</t>
-  </si>
-  <si>
-    <t>2025年07月27日 12:00</t>
-  </si>
-  <si>
-    <t>2025年07月27日 17:00</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>跟十堰田总前往襄阳中车集团公司总结凌特样车的遗留历史问题</t>
-  </si>
-  <si>
-    <t>202507300045</t>
-  </si>
-  <si>
-    <t>叶旭|发起审批|2025-07-30 17:35:17;张健宁|同意|2025-07-30 18:49:22;杜鸣|同意|2025-07-31 08:18:11</t>
-  </si>
-  <si>
-    <t>14h42m53.961s</t>
-  </si>
-  <si>
-    <t>2025年07月29日 19:00</t>
+    <t>开会以及编写会议纪要</t>
+  </si>
+  <si>
+    <t>202508200037</t>
+  </si>
+  <si>
+    <t>李淑娜|发起审批|2025-08-20 19:16:55;桂治国|同意|2025-08-20 20:04:00;朱显斌|同意|2025-08-20 20:20:40;雷继彬|同意|2025-08-21 00:06:01</t>
+  </si>
+  <si>
+    <t>4h49m6.813s</t>
+  </si>
+  <si>
+    <t>2025年08月20日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月20日 19:15</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>核实4000新增图纸下发情况，更新订单评审表格</t>
+  </si>
+  <si>
+    <t>202508300004</t>
+  </si>
+  <si>
+    <t>朱泽利|发起审批|2025-08-30 19:09:50;石丁哲|同意|2025-08-31 10:52:09;雷继彬|同意|2025-08-31 22:39:14</t>
+  </si>
+  <si>
+    <t>27h29m24.476s</t>
+  </si>
+  <si>
+    <t>2025年08月30日</t>
+  </si>
+  <si>
+    <t>2025年08月30日 09:00</t>
+  </si>
+  <si>
+    <t>2025年08月30日 17:00</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>修改MBT牵引车头VCU匹配动力挂车的主挂协同程序</t>
+  </si>
+  <si>
+    <t>202509020022</t>
+  </si>
+  <si>
+    <t>审批中</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-09-02 14:44:31;张健宁|同意|2025-09-02 16:23:16</t>
+  </si>
+  <si>
+    <t>杜鸣</t>
+  </si>
+  <si>
+    <t>2025年09月01日</t>
+  </si>
+  <si>
+    <t>2025年09月01日 18:30</t>
+  </si>
+  <si>
+    <t>2025年09月01日 20:00</t>
+  </si>
+  <si>
+    <t>杭州仓储与随州仓储账务处理</t>
+  </si>
+  <si>
+    <t>202509010043</t>
+  </si>
+  <si>
+    <t>梁梅|发起审批|2025-09-01 17:55:51;张健宁|同意|2025-09-01 17:56:21;杜鸣|同意|2025-09-02 08:38:46</t>
+  </si>
+  <si>
+    <t>14h42m55.329s</t>
+  </si>
+  <si>
+    <t>2025年08月29日</t>
+  </si>
+  <si>
+    <t>2025年08月29日 18:00</t>
+  </si>
+  <si>
+    <t>2025年08月29日 19:00</t>
   </si>
 </sst>
 </file>
@@ -1099,10 +1285,10 @@
         <v>27</v>
       </c>
       <c r="D3" s="1">
-        <v>45840.34674777778</v>
+        <v>45871.345601898145</v>
       </c>
       <c r="E3" s="1">
-        <v>45840.60160317129</v>
+        <v>45871.61132192129</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>28</v>
@@ -1173,34 +1359,34 @@
         <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1">
+        <v>45871.80796225694</v>
+      </c>
+      <c r="E4" s="1">
+        <v>45873.43207241898</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="1">
-        <v>45848.71118045139</v>
-      </c>
-      <c r="E4" s="1">
-        <v>45848.711800324076</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>28</v>
@@ -1212,31 +1398,31 @@
         <v>28</v>
       </c>
       <c r="P4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>51</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>28</v>
@@ -1244,7 +1430,7 @@
     </row>
     <row r="5" ht="20" customHeight="true">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
@@ -1253,67 +1439,67 @@
         <v>27</v>
       </c>
       <c r="D5" s="1">
-        <v>45840.69624653935</v>
+        <v>45868.73283862269</v>
       </c>
       <c r="E5" s="1">
-        <v>45840.843640150466</v>
+        <v>45869.3459631713</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>2</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>28</v>
@@ -1321,7 +1507,7 @@
     </row>
     <row r="6" ht="20" customHeight="true">
       <c r="A6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>20</v>
@@ -1330,49 +1516,49 @@
         <v>27</v>
       </c>
       <c r="D6" s="1">
-        <v>45841.5826540625</v>
+        <v>45871.808237916666</v>
       </c>
       <c r="E6" s="1">
-        <v>45841.58362239583</v>
+        <v>45873.43214788195</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>2</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>2</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>37</v>
@@ -1381,16 +1567,16 @@
         <v>38</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="W6" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Y6" s="2" t="s">
         <v>28</v>
@@ -1398,7 +1584,7 @@
     </row>
     <row r="7" ht="20" customHeight="true">
       <c r="A7" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>20</v>
@@ -1407,37 +1593,37 @@
         <v>27</v>
       </c>
       <c r="D7" s="1">
-        <v>45847.756702453706</v>
+        <v>45865.778988252314</v>
       </c>
       <c r="E7" s="1">
-        <v>45848.34990782407</v>
+        <v>45867.360394780095</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="L7" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1449,25 +1635,25 @@
         <v>2</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>28</v>
@@ -1475,7 +1661,7 @@
     </row>
     <row r="8" ht="20" customHeight="true">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>20</v>
@@ -1484,37 +1670,37 @@
         <v>27</v>
       </c>
       <c r="D8" s="1">
-        <v>45843.32336751158</v>
+        <v>45872.652376805556</v>
       </c>
       <c r="E8" s="1">
-        <v>45843.671769155095</v>
+        <v>45873.68924706019</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1526,25 +1712,25 @@
         <v>2</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>28</v>
@@ -1552,76 +1738,76 @@
     </row>
     <row r="9" ht="20" customHeight="true">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1">
-        <v>45843.36163777778</v>
+        <v>45868.362272164355</v>
       </c>
       <c r="E9" s="1">
-        <v>45845.487682418985</v>
+        <v>45869.345761585646</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="O9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>2</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="S9" s="2" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X9" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>28</v>
@@ -1629,76 +1815,76 @@
     </row>
     <row r="10" ht="20" customHeight="true">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1">
-        <v>45848.712818182874</v>
+        <v>45868.362272164355</v>
       </c>
       <c r="E10" s="1">
-        <v>45848.723491585646</v>
+        <v>45869.345761585646</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="M10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P10" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>28</v>
@@ -1706,76 +1892,76 @@
     </row>
     <row r="11" ht="20" customHeight="true">
       <c r="A11" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1">
-        <v>45848.7149681713</v>
+        <v>45866.77588552083</v>
       </c>
       <c r="E11" s="1">
-        <v>45848.7232734375</v>
+        <v>45867.462097083335</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>101</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X11" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>28</v>
@@ -1789,32 +1975,32 @@
         <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45876.754960162034</v>
+      </c>
+      <c r="E12" s="1">
+        <v>45876.75506287037</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="1">
-        <v>45848.71645141204</v>
-      </c>
-      <c r="E12" s="1">
-        <v>45848.72310877315</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="L12" s="2" t="s">
         <v>28</v>
       </c>
@@ -1822,7 +2008,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1834,25 +2020,25 @@
         <v>0</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>28</v>
@@ -1866,34 +2052,34 @@
         <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="D13" s="1">
-        <v>45855.754348599534</v>
+        <v>45876.75422943287</v>
       </c>
       <c r="E13" s="1">
-        <v>45856.37010594908</v>
+        <v>45876.75450935185</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>28</v>
@@ -1905,31 +2091,31 @@
         <v>28</v>
       </c>
       <c r="P13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>121</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="W13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="X13" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>28</v>
@@ -1946,31 +2132,31 @@
         <v>27</v>
       </c>
       <c r="D14" s="1">
-        <v>45850.84913701389</v>
+        <v>45876.75465951389</v>
       </c>
       <c r="E14" s="1">
-        <v>45851.90470865741</v>
+        <v>45876.88097042824</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>28</v>
@@ -1991,22 +2177,22 @@
         <v>127</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="V14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="V14" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="W14" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>28</v>
@@ -2014,7 +2200,7 @@
     </row>
     <row r="15" ht="20" customHeight="true">
       <c r="A15" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>20</v>
@@ -2023,37 +2209,37 @@
         <v>27</v>
       </c>
       <c r="D15" s="1">
-        <v>45861.367633738424</v>
+        <v>45872.65454989584</v>
       </c>
       <c r="E15" s="1">
-        <v>45861.63354638889</v>
+        <v>45873.689369155094</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -2065,25 +2251,25 @@
         <v>2</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="Y15" s="2" t="s">
         <v>28</v>
@@ -2091,7 +2277,7 @@
     </row>
     <row r="16" ht="20" customHeight="true">
       <c r="A16" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
@@ -2100,37 +2286,37 @@
         <v>27</v>
       </c>
       <c r="D16" s="1">
-        <v>45862.43760917824</v>
+        <v>45872.65454989584</v>
       </c>
       <c r="E16" s="1">
-        <v>45862.660600219904</v>
+        <v>45873.689369155094</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -2142,25 +2328,25 @@
         <v>2</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>28</v>
@@ -2168,46 +2354,46 @@
     </row>
     <row r="17" ht="20" customHeight="true">
       <c r="A17" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1">
-        <v>45848.71409070602</v>
+        <v>45872.65454989584</v>
       </c>
       <c r="E17" s="1">
-        <v>45848.723378090275</v>
+        <v>45873.689369155094</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="M17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2216,28 +2402,28 @@
         <v>2</v>
       </c>
       <c r="Q17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>28</v>
@@ -2245,7 +2431,7 @@
     </row>
     <row r="18" ht="20" customHeight="true">
       <c r="A18" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>20</v>
@@ -2254,37 +2440,37 @@
         <v>27</v>
       </c>
       <c r="D18" s="1">
-        <v>45862.76985383102</v>
+        <v>45876.75522741898</v>
       </c>
       <c r="E18" s="1">
-        <v>45863.6506683912</v>
+        <v>45876.8810409375</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2296,25 +2482,25 @@
         <v>2</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>28</v>
@@ -2322,7 +2508,7 @@
     </row>
     <row r="19" ht="20" customHeight="true">
       <c r="A19" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>20</v>
@@ -2331,37 +2517,37 @@
         <v>27</v>
       </c>
       <c r="D19" s="1">
-        <v>45850.98285706018</v>
+        <v>45878.75155248843</v>
       </c>
       <c r="E19" s="1">
-        <v>45851.43442900463</v>
+        <v>45880.62543201389</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="M19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -2373,25 +2559,25 @@
         <v>2</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>28</v>
@@ -2399,7 +2585,7 @@
     </row>
     <row r="20" ht="20" customHeight="true">
       <c r="A20" s="2" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>20</v>
@@ -2408,37 +2594,37 @@
         <v>27</v>
       </c>
       <c r="D20" s="1">
-        <v>45863.38679179398</v>
+        <v>45876.35292758102</v>
       </c>
       <c r="E20" s="1">
-        <v>45863.65041627315</v>
+        <v>45876.797802800924</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2450,25 +2636,25 @@
         <v>2</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>28</v>
@@ -2476,7 +2662,7 @@
     </row>
     <row r="21" ht="20" customHeight="true">
       <c r="A21" s="2" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>20</v>
@@ -2485,37 +2671,37 @@
         <v>27</v>
       </c>
       <c r="D21" s="1">
-        <v>45862.845371296295</v>
+        <v>45876.35292758102</v>
       </c>
       <c r="E21" s="1">
-        <v>45863.65061449074</v>
+        <v>45876.797802800924</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2527,25 +2713,25 @@
         <v>2</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>28</v>
@@ -2553,7 +2739,7 @@
     </row>
     <row r="22" ht="20" customHeight="true">
       <c r="A22" s="2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>20</v>
@@ -2562,37 +2748,37 @@
         <v>27</v>
       </c>
       <c r="D22" s="1">
-        <v>45868.362272164355</v>
+        <v>45878.788503055555</v>
       </c>
       <c r="E22" s="1">
-        <v>45869.345761585646</v>
+        <v>45880.62529804398</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2604,25 +2790,25 @@
         <v>2</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>28</v>
@@ -2630,7 +2816,7 @@
     </row>
     <row r="23" ht="20" customHeight="true">
       <c r="A23" s="2" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>20</v>
@@ -2639,37 +2825,37 @@
         <v>27</v>
       </c>
       <c r="D23" s="1">
-        <v>45868.362272164355</v>
+        <v>45884.350086701386</v>
       </c>
       <c r="E23" s="1">
-        <v>45869.345761585646</v>
+        <v>45884.596022997684</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2681,25 +2867,25 @@
         <v>2</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>28</v>
@@ -2707,7 +2893,7 @@
     </row>
     <row r="24" ht="20" customHeight="true">
       <c r="A24" s="2" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>20</v>
@@ -2716,37 +2902,37 @@
         <v>27</v>
       </c>
       <c r="D24" s="1">
-        <v>45866.77588552083</v>
+        <v>45882.75805231481</v>
       </c>
       <c r="E24" s="1">
-        <v>45867.462097083335</v>
+        <v>45883.430759016206</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="M24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2758,25 +2944,25 @@
         <v>2</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>193</v>
+        <v>55</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>28</v>
@@ -2784,7 +2970,7 @@
     </row>
     <row r="25" ht="20" customHeight="true">
       <c r="A25" s="2" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>20</v>
@@ -2793,37 +2979,37 @@
         <v>27</v>
       </c>
       <c r="D25" s="1">
-        <v>45865.778988252314</v>
+        <v>45878.86772101852</v>
       </c>
       <c r="E25" s="1">
-        <v>45867.360394780095</v>
+        <v>45879.96112733796</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>197</v>
+        <v>49</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2835,25 +3021,25 @@
         <v>2</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>38</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>203</v>
+        <v>90</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>28</v>
@@ -2861,7 +3047,7 @@
     </row>
     <row r="26" ht="20" customHeight="true">
       <c r="A26" s="2" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>20</v>
@@ -2870,19 +3056,19 @@
         <v>27</v>
       </c>
       <c r="D26" s="1">
-        <v>45868.73283862269</v>
+        <v>45880.83797813657</v>
       </c>
       <c r="E26" s="1">
-        <v>45869.3459631713</v>
+        <v>45881.431267789354</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>31</v>
@@ -2894,28 +3080,28 @@
         <v>33</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="P26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>38</v>
@@ -2924,15 +3110,1014 @@
         <v>185</v>
       </c>
       <c r="V26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="true">
+      <c r="A27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="1">
+        <v>45885.45750511574</v>
+      </c>
+      <c r="E27" s="1">
+        <v>45885.52526449074</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="true">
+      <c r="A28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="1">
+        <v>45885.52614796296</v>
+      </c>
+      <c r="E28" s="1">
+        <v>45885.527993587966</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="true">
+      <c r="A29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1">
+        <v>45882.76356670139</v>
+      </c>
+      <c r="E29" s="1">
+        <v>45882.77342597222</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>3</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="true">
+      <c r="A30" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="1">
+        <v>45885.331969224535</v>
+      </c>
+      <c r="E30" s="1">
+        <v>45885.45716978009</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="O30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="true">
+      <c r="A31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1">
+        <v>45885.52811912037</v>
+      </c>
+      <c r="E31" s="1">
+        <v>45887.44849425926</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>2</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="W31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="true">
+      <c r="A32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>45889.35449373843</v>
+      </c>
+      <c r="E32" s="1">
+        <v>45889.38039054398</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>2</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="true">
+      <c r="A33" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="1">
+        <v>45885.88539537037</v>
+      </c>
+      <c r="E33" s="1">
+        <v>45889.43590174768</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="true">
+      <c r="A34" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="1">
+        <v>45889.391104386574</v>
+      </c>
+      <c r="E34" s="1">
+        <v>45889.41616395833</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>2</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="true">
+      <c r="A35" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="1">
+        <v>45894.87793126157</v>
+      </c>
+      <c r="E35" s="1">
+        <v>45895.36718180556</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>3</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="true">
+      <c r="A36" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="1">
+        <v>45889.8034146412</v>
+      </c>
+      <c r="E36" s="1">
+        <v>45890.00418793981</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>3</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y36" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="true">
+      <c r="A37" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="1">
+        <v>45899.79850575232</v>
+      </c>
+      <c r="E37" s="1">
+        <v>45900.94392792824</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="X26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y26" s="2" t="s">
+      <c r="H37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>2</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="true">
+      <c r="A38" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D38" s="1">
+        <v>45902.61425540509</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="P38" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>1</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="true">
+      <c r="A39" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="1">
+        <v>45901.747126030095</v>
+      </c>
+      <c r="E39" s="1">
+        <v>45902.36026641203</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>2</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y39" s="2" t="s">
         <v>28</v>
       </c>
     </row>
